--- a/artfynd/A 39507-2022 artfynd.xlsx
+++ b/artfynd/A 39507-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39507-2022 artfynd.xlsx
+++ b/artfynd/A 39507-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96340380</v>
+        <v>96340126</v>
       </c>
       <c r="B2" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,9 +715,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -730,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>413509.0507753213</v>
+        <v>413606</v>
       </c>
       <c r="R2" t="n">
-        <v>6260001.691750403</v>
+        <v>6260072</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -763,19 +759,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -808,15 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96340302</v>
+        <v>96340145</v>
       </c>
       <c r="B3" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,26 +805,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -853,9 +834,10 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -863,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>413507.0862815973</v>
+        <v>413609</v>
       </c>
       <c r="R3" t="n">
-        <v>6259986.817684759</v>
+        <v>6260076</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -896,19 +878,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -944,12 +916,7 @@
         <v>96340318</v>
       </c>
       <c r="B4" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>413505.9345806667</v>
+        <v>413506</v>
       </c>
       <c r="R4" t="n">
-        <v>6259984.631703123</v>
+        <v>6259985</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1030,19 +997,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1075,15 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96340261</v>
+        <v>96340365</v>
       </c>
       <c r="B5" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,38 +1043,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>cm²</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1130,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>413521.9116296514</v>
+        <v>413498</v>
       </c>
       <c r="R5" t="n">
-        <v>6260008.057480088</v>
+        <v>6260026</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1163,19 +1116,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1208,15 +1151,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96340242</v>
+        <v>96340425</v>
       </c>
       <c r="B6" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,26 +1162,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1253,9 +1191,10 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1263,10 +1202,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>413547.9496610333</v>
+        <v>413544</v>
       </c>
       <c r="R6" t="n">
-        <v>6260009.182681695</v>
+        <v>6260016</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1296,19 +1235,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1341,15 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96340176</v>
+        <v>96340154</v>
       </c>
       <c r="B7" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1357,26 +1281,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1384,11 +1308,8 @@
           <t>dm²</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1396,10 +1317,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>413567.3242031019</v>
+        <v>413609</v>
       </c>
       <c r="R7" t="n">
-        <v>6260063.47184745</v>
+        <v>6260076</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1429,19 +1350,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1474,15 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96340430</v>
+        <v>96340106</v>
       </c>
       <c r="B8" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1509,7 +1415,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1529,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>413548.773611602</v>
+        <v>413606</v>
       </c>
       <c r="R8" t="n">
-        <v>6260022.422854268</v>
+        <v>6260072</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1562,24 +1468,14 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en levande bok</t>
+          <t>På en levande bok.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1607,15 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96340223</v>
+        <v>96340166</v>
       </c>
       <c r="B9" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1662,10 +1553,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>413552.6240088855</v>
+        <v>413558</v>
       </c>
       <c r="R9" t="n">
-        <v>6260021.239460511</v>
+        <v>6260069</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1695,24 +1586,14 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>En döende bok</t>
+          <t>På en levande bok</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1740,15 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96340425</v>
+        <v>96340176</v>
       </c>
       <c r="B10" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1756,26 +1632,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1785,10 +1661,9 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1796,10 +1671,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>413543.6700376791</v>
+        <v>413567</v>
       </c>
       <c r="R10" t="n">
-        <v>6260016.450980085</v>
+        <v>6260063</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1829,19 +1704,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1874,15 +1739,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96340389</v>
+        <v>96340189</v>
       </c>
       <c r="B11" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1909,7 +1769,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1929,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>413524.9036540196</v>
+        <v>413569</v>
       </c>
       <c r="R11" t="n">
-        <v>6260019.043859304</v>
+        <v>6260026</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1962,19 +1822,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -2007,15 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96340365</v>
+        <v>96340204</v>
       </c>
       <c r="B12" t="n">
-        <v>95198</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2023,26 +1868,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2052,10 +1897,9 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>utan kapsel</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -2063,10 +1907,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>413498.4703760776</v>
+        <v>413565</v>
       </c>
       <c r="R12" t="n">
-        <v>6260025.660127493</v>
+        <v>6260024</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2096,19 +1940,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2141,15 +1975,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96340329</v>
+        <v>96340223</v>
       </c>
       <c r="B13" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2176,7 +2005,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2196,10 +2025,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>413501.158139644</v>
+        <v>413553</v>
       </c>
       <c r="R13" t="n">
-        <v>6259994.672133162</v>
+        <v>6260021</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2229,24 +2058,14 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På en levande bok</t>
+          <t>En döende bok</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2274,15 +2093,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96340404</v>
+        <v>96340242</v>
       </c>
       <c r="B14" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2329,10 +2143,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>413536.5450792604</v>
+        <v>413548</v>
       </c>
       <c r="R14" t="n">
-        <v>6260019.91077553</v>
+        <v>6260009</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2362,19 +2176,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -2407,15 +2211,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96340351</v>
+        <v>96340261</v>
       </c>
       <c r="B15" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2442,12 +2241,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>cm²</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2462,10 +2261,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>413483.4415654204</v>
+        <v>413522</v>
       </c>
       <c r="R15" t="n">
-        <v>6260021.548310673</v>
+        <v>6260008</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2495,19 +2294,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2543,12 +2332,7 @@
         <v>96340281</v>
       </c>
       <c r="B16" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2595,10 +2379,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>413511.1285084666</v>
+        <v>413511</v>
       </c>
       <c r="R16" t="n">
-        <v>6259995.020761346</v>
+        <v>6259995</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2628,19 +2412,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2673,15 +2447,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96340166</v>
+        <v>96340302</v>
       </c>
       <c r="B17" t="n">
-        <v>79104</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80992</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2708,7 +2477,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2728,10 +2497,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>413558.0313216612</v>
+        <v>413507</v>
       </c>
       <c r="R17" t="n">
-        <v>6260069.185317496</v>
+        <v>6259987</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2761,19 +2530,9 @@
           <t>2021-09-27</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-09-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2803,6 +2562,714 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>96340329</v>
+      </c>
+      <c r="B18" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>413501</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6259995</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>96340351</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>413483</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6260022</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>96340380</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>413509</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6260002</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>96340389</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>413525</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6260019</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>96340404</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>413537</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6260020</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>96340430</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Prästtorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>413549</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6260022</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Markaryd</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2021-09-27</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en levande bok</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Krister Wahlström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39507-2022 artfynd.xlsx
+++ b/artfynd/A 39507-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -910,6 +920,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340318</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1148,6 +1168,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340365</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1267,6 +1292,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340425</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1382,6 +1412,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340154</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1500,6 +1535,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340106</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1618,6 +1658,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340166</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1736,6 +1781,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340176</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1854,6 +1904,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340189</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1972,6 +2027,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340204</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2090,6 +2150,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340223</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2208,6 +2273,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340242</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2326,6 +2396,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340261</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2444,6 +2519,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340281</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2562,6 +2642,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340302</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2680,6 +2765,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340329</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2798,6 +2888,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340351</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2916,6 +3011,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340380</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3034,6 +3134,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340389</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3152,6 +3257,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340404</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3270,8 +3380,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96340430</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>